--- a/Changes Tracking.xlsx
+++ b/Changes Tracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilytyszka/Desktop/Research/Reich Lab/Allocation Score/Allocation Score Manuscript/utility-eval-papers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA358143-DFDD-334A-9249-4646418BE7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7465AFB5-AC6D-7848-89FE-1737F607CDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="14780" activeTab="1" xr2:uid="{11C9D71A-4E8A-6B49-B8E8-C5CA3E3420D0}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Coding Changes" sheetId="1" r:id="rId1"/>
     <sheet name="Writing Changes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>Date</t>
   </si>
@@ -636,6 +636,123 @@
   </si>
   <si>
     <t>Introduction</t>
+  </si>
+  <si>
+    <t>Methods, Discussion</t>
+  </si>
+  <si>
+    <t>Goal to get a first run methods and start discussion</t>
+  </si>
+  <si>
+    <t>Chipping away…....</t>
+  </si>
+  <si>
+    <t>Chipping away…</t>
+  </si>
+  <si>
+    <t>Finally expressed the probabilistic procedure in words (woohoo)</t>
+  </si>
+  <si>
+    <t>Discussion</t>
+  </si>
+  <si>
+    <t>Discussion, conclusions</t>
+  </si>
+  <si>
+    <t>Edited yesterday's discussion work, conclusion brainstorming</t>
+  </si>
+  <si>
+    <t>Conclusions, overall edits</t>
+  </si>
+  <si>
+    <t>Editing. Tried to bang out conclusions</t>
+  </si>
+  <si>
+    <t>Overall edits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edited everything - especially conclusions. </t>
+  </si>
+  <si>
+    <t>Really needs citations + first part of intro smoothing + abstract</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created new document: Journal Submission Brainstorming </t>
+  </si>
+  <si>
+    <t>Lists possible journals</t>
+  </si>
+  <si>
+    <t>Finished list in anticipation of meeting. Created new document: Draft 2 (work in Draft 2 from here on out). Revised normal weighting as per Nick's recommendations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Big sweep to impliment Nick's </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in-document</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> edits</t>
+    </r>
+  </si>
+  <si>
+    <t>Next step: big sweep of everything we talked over in our meeting. I just needed to get all of this out of the way.</t>
+  </si>
+  <si>
+    <t>Overall edits - mostly intro and methods</t>
+  </si>
+  <si>
+    <t>Overall edits - mostly intro</t>
+  </si>
+  <si>
+    <t>Results (and Methods)</t>
+  </si>
+  <si>
+    <t>Add and describe the baseline 50th distribution</t>
+  </si>
+  <si>
+    <t>baseline-50.R, _targets.R</t>
+  </si>
+  <si>
+    <t>Similar scheme to per-capita, but uses the baseline model's 0.500 quantile (aka uses recent case counts to scale, with no prediction interval)</t>
+  </si>
+  <si>
+    <t>Add the baseline 50th distribution (recent-case-counts)</t>
+  </si>
+  <si>
+    <t>Captions overhaul; graph tweaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After meeting with Nick - some fixes. </t>
+  </si>
+  <si>
+    <t>Make mean rank plot</t>
+  </si>
+  <si>
+    <t>Overhaul of results</t>
+  </si>
+  <si>
+    <t>Issue with FAIR-NRAR in the 1 week horizon? Diagnose tomorrow</t>
+  </si>
+  <si>
+    <t>Diagnose FAIR-NRAR 1 week issue?</t>
   </si>
 </sst>
 </file>
@@ -643,9 +760,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="mm/dd/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -694,12 +811,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="9"/>
       <name val="Aptos Narrow"/>
@@ -721,6 +832,19 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -754,8 +878,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -763,18 +887,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1514,6 +1638,20 @@
         <v>104</v>
       </c>
     </row>
+    <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>23</v>
@@ -1680,7 +1818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E2AFCB-4226-884F-968E-05300729E6C6}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1885,12 +2023,186 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>46227</v>
       </c>
       <c r="B18" t="s">
         <v>120</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>46241</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="C32" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="C33" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
